--- a/factory/工厂配送兔司家门店客户月度业绩对比表_格式化模板.xlsx
+++ b/factory/工厂配送兔司家门店客户月度业绩对比表_格式化模板.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6ACE02-A753-4C25-BE69-AB446186779A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81859974-CA81-468B-B1DA-DAE47B0766B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="配送门店业绩表 5.1-5.31" sheetId="4" r:id="rId1"/>
+    <sheet name="2026年5月1日至5月31日兔司家客户月度业绩对比表" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -109,7 +109,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">2026年5月1日至5月31日工厂配送兔司家门店货款统计表
+      <t xml:space="preserve">2026年5月1日至5月31日工厂配送兔司家门店客户月度业绩对比表
 </t>
     </r>
     <r>
